--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>204</v>
+        <v>298</v>
       </c>
       <c r="D2">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="E2">
-        <v>117</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>165</v>
+        <v>289</v>
       </c>
       <c r="D3">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E3">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="D3">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H3">
         <v>426</v>
